--- a/import/BOT1_Veranstaltungsliste.xlsx
+++ b/import/BOT1_Veranstaltungsliste.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20394"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\+++Schule\AE_LF12\Projekt Berufsorientierungstag\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{138B5649-8413-4F6E-9D0E-902A61ECF0DB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B9DB874-C440-4C65-8C4D-4F4AE736D97F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" xr2:uid="{3A9E2240-F68F-4045-AE50-B76F133D2F1C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{3A9E2240-F68F-4045-AE50-B76F133D2F1C}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -162,9 +162,6 @@
     <t>Max. Teilnehmer</t>
   </si>
   <si>
-    <t>Max. Veranstaltungen</t>
-  </si>
-  <si>
     <t>Frühester Zeitpunkt</t>
   </si>
   <si>
@@ -187,6 +184,9 @@
   </si>
   <si>
     <t>B</t>
+  </si>
+  <si>
+    <t>Min.</t>
   </si>
 </sst>
 </file>
@@ -581,10 +581,10 @@
         <v>44</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -604,7 +604,7 @@
         <v>5</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -624,7 +624,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -644,7 +644,7 @@
         <v>5</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="45" x14ac:dyDescent="0.25">
@@ -655,7 +655,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D5" s="1">
         <v>20</v>
@@ -664,7 +664,7 @@
         <v>5</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -684,7 +684,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -704,7 +704,7 @@
         <v>5</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -715,7 +715,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D8" s="1">
         <v>20</v>
@@ -724,7 +724,7 @@
         <v>5</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -744,7 +744,7 @@
         <v>5</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -764,7 +764,7 @@
         <v>5</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -784,7 +784,7 @@
         <v>5</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -804,7 +804,7 @@
         <v>5</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -824,7 +824,7 @@
         <v>5</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -844,7 +844,7 @@
         <v>5</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -855,7 +855,7 @@
         <v>14</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D15" s="1">
         <v>20</v>
@@ -864,7 +864,7 @@
         <v>5</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -884,7 +884,7 @@
         <v>5</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -904,7 +904,7 @@
         <v>5</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -915,7 +915,7 @@
         <v>38</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D18" s="1">
         <v>20</v>
@@ -924,7 +924,7 @@
         <v>5</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -944,7 +944,7 @@
         <v>5</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -964,7 +964,7 @@
         <v>5</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -975,7 +975,7 @@
         <v>17</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D21" s="1">
         <v>20</v>
@@ -984,7 +984,7 @@
         <v>5</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1004,7 +1004,7 @@
         <v>5</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1024,7 +1024,7 @@
         <v>5</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1041,7 +1041,7 @@
         <v>5</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -1061,7 +1061,7 @@
         <v>5</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1078,7 +1078,7 @@
         <v>5</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -1095,7 +1095,7 @@
         <v>5</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1112,7 +1112,7 @@
         <v>5</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/import/BOT1_Veranstaltungsliste.xlsx
+++ b/import/BOT1_Veranstaltungsliste.xlsx
@@ -183,7 +183,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -193,6 +193,12 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -232,7 +238,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -249,11 +255,14 @@
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general" wrapText="1"/>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general" wrapText="1"/>
@@ -565,7 +574,7 @@
   <cols>
     <col min="1" max="1" style="7" width="4.147857142857143" customWidth="1" bestFit="1"/>
     <col min="2" max="2" style="8" width="30.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="8" width="38.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="9" width="38.43357142857143" customWidth="1" bestFit="1"/>
     <col min="4" max="4" style="7" width="11.290714285714287" customWidth="1" bestFit="1"/>
     <col min="5" max="5" style="7" width="17.719285714285714" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="8" width="18.719285714285714" customWidth="1" bestFit="1"/>
@@ -591,7 +600,7 @@
         <v>5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="17.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -605,13 +614,13 @@
         <v>20</v>
       </c>
       <c r="E2" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="17.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -631,7 +640,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="17.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -645,13 +654,13 @@
         <v>20</v>
       </c>
       <c r="E4" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="39.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="46.5" customFormat="1" s="1">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -671,7 +680,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="17.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -691,7 +700,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="17.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -711,7 +720,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="28.5" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="33" customFormat="1" s="1">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -731,7 +740,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="17.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -751,7 +760,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="17.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -771,7 +780,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="17.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="33" customFormat="1" s="1">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -791,7 +800,7 @@
         <v>24</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="17.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -811,7 +820,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="17.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -831,7 +840,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="17.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -851,7 +860,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="28.5" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="33" customFormat="1" s="1">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -871,7 +880,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="17.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -891,7 +900,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="17.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A17" s="4">
         <v>16</v>
       </c>
@@ -911,7 +920,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="28.5" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="33" customFormat="1" s="1">
       <c r="A18" s="4">
         <v>17</v>
       </c>
@@ -931,7 +940,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="17.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A19" s="4">
         <v>18</v>
       </c>
@@ -951,7 +960,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="17.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A20" s="4">
         <v>19</v>
       </c>
@@ -971,7 +980,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="28.5" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="33" customFormat="1" s="1">
       <c r="A21" s="4">
         <v>20</v>
       </c>
@@ -991,7 +1000,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="28.5" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="33" customFormat="1" s="1">
       <c r="A22" s="4">
         <v>21</v>
       </c>
@@ -1011,7 +1020,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="17.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A23" s="4">
         <v>22</v>
       </c>
@@ -1031,7 +1040,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="17.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A24" s="4">
         <v>23</v>
       </c>
@@ -1049,7 +1058,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="28.5" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="33" customFormat="1" s="1">
       <c r="A25" s="4">
         <v>24</v>
       </c>
@@ -1069,7 +1078,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="17.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A26" s="4">
         <v>25</v>
       </c>
@@ -1087,7 +1096,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="17.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A27" s="4">
         <v>26</v>
       </c>
